--- a/data/macro/China/China PMI.xlsx
+++ b/data/macro/China/China PMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD81C6E-C64B-4D42-8B64-1BC9DF92FCDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC13EB3-2128-41C8-82F1-6F515FC513D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4785" yWindow="3780" windowWidth="27240" windowHeight="16185" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -78,8 +78,8 @@
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -164,16 +164,16 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -514,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8641136A-8358-754A-BFC1-48B8F9996351}">
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:G255"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="4" bestFit="1" customWidth="1"/>
@@ -6365,6 +6365,26 @@
       </c>
       <c r="G254" s="9">
         <v>50.1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A255" s="4">
+        <v>46054</v>
+      </c>
+      <c r="B255" s="4">
+        <v>46085</v>
+      </c>
+      <c r="C255" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F255" s="9">
+        <v>49.1</v>
+      </c>
+      <c r="G255" s="9">
+        <v>49.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/China/China PMI.xlsx
+++ b/data/macro/China/China PMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC13EB3-2128-41C8-82F1-6F515FC513D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E249130F-D2F8-4EBA-BAA5-CDE8FCAC07BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="3780" windowWidth="27240" windowHeight="16185" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
   <sheets>
     <sheet name="CPMINDX" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -514,15 +514,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8641136A-8358-754A-BFC1-48B8F9996351}">
-  <dimension ref="A1:G255"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G257"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="10"/>
-    <col min="5" max="7" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="3"/>
+    <col min="1" max="1" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="10"/>
+    <col min="5" max="7" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.54296875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -6380,6 +6380,9 @@
       <c r="D255" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="E255" s="9">
+        <v>49</v>
+      </c>
       <c r="F255" s="9">
         <v>49.1</v>
       </c>
@@ -6387,8 +6390,48 @@
         <v>49.3</v>
       </c>
     </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A256" s="4">
+        <v>46082</v>
+      </c>
+      <c r="B256" s="4">
+        <v>46112</v>
+      </c>
+      <c r="C256" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" s="9">
+        <v>50.4</v>
+      </c>
+      <c r="F256" s="9">
+        <v>50.1</v>
+      </c>
+      <c r="G256" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A257" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B257" s="4">
+        <v>46142</v>
+      </c>
+      <c r="C257" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="9">
+        <v>50.4</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G253">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G253">
     <sortCondition ref="B2:B253"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6400,9 +6443,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443F9EE-BDA7-42C7-BB47-C54379F4610C}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -6410,7 +6453,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>9</v>
       </c>

--- a/data/macro/China/China PMI.xlsx
+++ b/data/macro/China/China PMI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E249130F-D2F8-4EBA-BAA5-CDE8FCAC07BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF71E575-3E63-40C3-9402-6CF02606DFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
@@ -6426,6 +6426,12 @@
       <c r="D257" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="E257" s="9">
+        <v>50.3</v>
+      </c>
+      <c r="F257" s="9">
+        <v>50.1</v>
+      </c>
       <c r="G257" s="9">
         <v>50.4</v>
       </c>
